--- a/PC_2009/AS_031.xlsx
+++ b/PC_2009/AS_031.xlsx
@@ -17,7 +17,7 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="5">
+  <fonts count="6">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -45,8 +45,14 @@
     <font>
       <b val="1"/>
     </font>
+    <font>
+      <name val="Calibri"/>
+      <b val="1"/>
+      <color rgb="00000000"/>
+      <sz val="11"/>
+    </font>
   </fonts>
-  <fills count="3">
+  <fills count="6">
     <fill>
       <patternFill/>
     </fill>
@@ -59,8 +65,26 @@
         <bgColor rgb="001F497D"/>
       </patternFill>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00FFF2CC"/>
+        <bgColor rgb="00FFF2CC"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00D9E1F2"/>
+        <bgColor rgb="00D9E1F2"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00E2EFDA"/>
+        <bgColor rgb="00E2EFDA"/>
+      </patternFill>
+    </fill>
   </fills>
-  <borders count="2">
+  <borders count="5">
     <border>
       <left/>
       <right/>
@@ -82,11 +106,53 @@
         <color rgb="00D9D9D9"/>
       </bottom>
     </border>
+    <border>
+      <left style="thin">
+        <color rgb="00D3D3D3"/>
+      </left>
+      <right style="thin">
+        <color rgb="00D3D3D3"/>
+      </right>
+      <top style="medium">
+        <color rgb="001B365D"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="00D3D3D3"/>
+      </bottom>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="00D3D3D3"/>
+      </left>
+      <right style="thin">
+        <color rgb="00D3D3D3"/>
+      </right>
+      <top style="thin">
+        <color rgb="00D3D3D3"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="00D3D3D3"/>
+      </bottom>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="00D3D3D3"/>
+      </left>
+      <right style="thin">
+        <color rgb="00D3D3D3"/>
+      </right>
+      <top style="thin">
+        <color rgb="00D3D3D3"/>
+      </top>
+      <bottom style="double">
+        <color rgb="001B365D"/>
+      </bottom>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="8">
+  <cellXfs count="17">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
@@ -102,6 +168,21 @@
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="3" borderId="2" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="2" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="3" fontId="5" fillId="3" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="4" borderId="3" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="3" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="3" fontId="5" fillId="4" borderId="3" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="5" borderId="4" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="5" borderId="4" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="3" fontId="5" fillId="5" borderId="4" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -468,7 +549,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:U279"/>
+  <dimension ref="A1:U281"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="35" customWidth="1" min="1" max="1"/>
@@ -511,6 +592,7 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr"/>
     </row>
+    <row r="4"/>
     <row r="5">
       <c r="A5" s="3" t="inlineStr">
         <is>
@@ -18944,81 +19026,235 @@
       </c>
     </row>
     <row r="279">
-      <c r="A279" s="6" t="inlineStr">
-        <is>
-          <t>TOTAL</t>
-        </is>
-      </c>
-      <c r="C279" s="7">
+      <c r="A279" s="8" t="inlineStr">
+        <is>
+          <t>TOTAL EVM VOTES</t>
+        </is>
+      </c>
+      <c r="B279" s="9" t="inlineStr"/>
+      <c r="C279" s="10">
         <f>SUM(C6:C278)</f>
         <v/>
       </c>
-      <c r="D279" s="7">
+      <c r="D279" s="10">
         <f>SUM(D6:D278)</f>
         <v/>
       </c>
-      <c r="E279" s="7">
+      <c r="E279" s="10">
         <f>SUM(E6:E278)</f>
         <v/>
       </c>
-      <c r="F279" s="7">
+      <c r="F279" s="10">
         <f>SUM(F6:F278)</f>
         <v/>
       </c>
-      <c r="G279" s="7">
+      <c r="G279" s="10">
         <f>SUM(G6:G278)</f>
         <v/>
       </c>
-      <c r="H279" s="7">
+      <c r="H279" s="10">
         <f>SUM(H6:H278)</f>
         <v/>
       </c>
-      <c r="I279" s="7">
+      <c r="I279" s="10">
         <f>SUM(I6:I278)</f>
         <v/>
       </c>
-      <c r="J279" s="7">
+      <c r="J279" s="10">
         <f>SUM(J6:J278)</f>
         <v/>
       </c>
-      <c r="K279" s="7">
+      <c r="K279" s="10">
         <f>SUM(K6:K278)</f>
         <v/>
       </c>
-      <c r="L279" s="7">
+      <c r="L279" s="10">
         <f>SUM(L6:L278)</f>
         <v/>
       </c>
-      <c r="M279" s="7">
+      <c r="M279" s="10">
         <f>SUM(M6:M278)</f>
         <v/>
       </c>
-      <c r="N279" s="7">
+      <c r="N279" s="10">
         <f>SUM(N6:N278)</f>
         <v/>
       </c>
-      <c r="O279" s="7">
+      <c r="O279" s="10">
         <f>SUM(O6:O278)</f>
         <v/>
       </c>
-      <c r="P279" s="7">
+      <c r="P279" s="10">
         <f>SUM(P6:P278)</f>
         <v/>
       </c>
-      <c r="Q279" s="7">
+      <c r="Q279" s="10">
         <f>SUM(Q6:Q278)</f>
         <v/>
       </c>
-      <c r="R279" s="7">
+      <c r="R279" s="10">
         <f>SUM(R6:R278)</f>
         <v/>
       </c>
-      <c r="S279" s="7">
+      <c r="S279" s="10">
         <f>SUM(S6:S278)</f>
         <v/>
       </c>
-      <c r="T279" s="7">
+      <c r="T279" s="10">
         <f>SUM(T6:T278)</f>
+        <v/>
+      </c>
+      <c r="U279" s="10">
+        <f>SUM(U6:U278)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="280">
+      <c r="A280" s="11" t="inlineStr">
+        <is>
+          <t>POSTAL BALLOT VOTES</t>
+        </is>
+      </c>
+      <c r="B280" s="12" t="inlineStr"/>
+      <c r="C280" s="13" t="n">
+        <v>0</v>
+      </c>
+      <c r="D280" s="13" t="n">
+        <v>0</v>
+      </c>
+      <c r="E280" s="13" t="n">
+        <v>0</v>
+      </c>
+      <c r="F280" s="13" t="n">
+        <v>0</v>
+      </c>
+      <c r="G280" s="13" t="n">
+        <v>0</v>
+      </c>
+      <c r="H280" s="13" t="n">
+        <v>0</v>
+      </c>
+      <c r="I280" s="13" t="n">
+        <v>0</v>
+      </c>
+      <c r="J280" s="13" t="n">
+        <v>0</v>
+      </c>
+      <c r="K280" s="13" t="n">
+        <v>0</v>
+      </c>
+      <c r="L280" s="13" t="n">
+        <v>0</v>
+      </c>
+      <c r="M280" s="13" t="n">
+        <v>0</v>
+      </c>
+      <c r="N280" s="13" t="n">
+        <v>0</v>
+      </c>
+      <c r="O280" s="13" t="n">
+        <v>0</v>
+      </c>
+      <c r="P280" s="13" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q280" s="13" t="n">
+        <v>0</v>
+      </c>
+      <c r="R280" s="13" t="n">
+        <v>0</v>
+      </c>
+      <c r="S280" s="13" t="n">
+        <v>0</v>
+      </c>
+      <c r="T280" s="13" t="n">
+        <v>0</v>
+      </c>
+      <c r="U280" s="13" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="281">
+      <c r="A281" s="14" t="inlineStr">
+        <is>
+          <t>TOTAL VOTES POLLED</t>
+        </is>
+      </c>
+      <c r="B281" s="15" t="inlineStr"/>
+      <c r="C281" s="16">
+        <f>C279+C280</f>
+        <v/>
+      </c>
+      <c r="D281" s="16">
+        <f>D279+D280</f>
+        <v/>
+      </c>
+      <c r="E281" s="16">
+        <f>E279+E280</f>
+        <v/>
+      </c>
+      <c r="F281" s="16">
+        <f>F279+F280</f>
+        <v/>
+      </c>
+      <c r="G281" s="16">
+        <f>G279+G280</f>
+        <v/>
+      </c>
+      <c r="H281" s="16">
+        <f>H279+H280</f>
+        <v/>
+      </c>
+      <c r="I281" s="16">
+        <f>I279+I280</f>
+        <v/>
+      </c>
+      <c r="J281" s="16">
+        <f>J279+J280</f>
+        <v/>
+      </c>
+      <c r="K281" s="16">
+        <f>K279+K280</f>
+        <v/>
+      </c>
+      <c r="L281" s="16">
+        <f>L279+L280</f>
+        <v/>
+      </c>
+      <c r="M281" s="16">
+        <f>M279+M280</f>
+        <v/>
+      </c>
+      <c r="N281" s="16">
+        <f>N279+N280</f>
+        <v/>
+      </c>
+      <c r="O281" s="16">
+        <f>O279+O280</f>
+        <v/>
+      </c>
+      <c r="P281" s="16">
+        <f>P279+P280</f>
+        <v/>
+      </c>
+      <c r="Q281" s="16">
+        <f>Q279+Q280</f>
+        <v/>
+      </c>
+      <c r="R281" s="16">
+        <f>R279+R280</f>
+        <v/>
+      </c>
+      <c r="S281" s="16">
+        <f>S279+S280</f>
+        <v/>
+      </c>
+      <c r="T281" s="16">
+        <f>T279+T280</f>
+        <v/>
+      </c>
+      <c r="U281" s="16">
+        <f>U279+U280</f>
         <v/>
       </c>
     </row>
